--- a/jira_export_2026-06-23.xlsx
+++ b/jira_export_2026-06-23.xlsx
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>44971.85</v>
       </c>
       <c r="P180" s="19" t="n">
-        <v>119.69</v>
+        <v>119.61</v>
       </c>
     </row>
   </sheetData>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>212.5</v>
+        <v>212.75</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>42</v>
@@ -14485,7 +14485,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>262.5</v>
+        <v>262.75</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>78</v>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-06-23.xlsx
+++ b/jira_export_2026-06-23.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>45,797 €</t>
+          <t>46,000 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>31,698 €</t>
+          <t>31,901 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>602 h</t>
+          <t>610 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -898,7 +898,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -6520,8 +6520,8 @@
       <c r="N81" s="13" t="n">
         <v>203.5</v>
       </c>
-      <c r="O81" s="14" t="n">
-        <v>0</v>
+      <c r="O81" s="13" t="n">
+        <v>203.5</v>
       </c>
       <c r="P81" s="13" t="n">
         <v>0</v>
@@ -11421,7 +11421,7 @@
         <v>18</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>10.25</v>
+        <v>11.75</v>
       </c>
       <c r="L151" s="12" t="inlineStr"/>
       <c r="M151" s="12" t="inlineStr"/>
@@ -12019,7 +12019,7 @@
         <v>28</v>
       </c>
       <c r="K160" s="16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="L160" s="16" t="inlineStr"/>
       <c r="M160" s="16" t="inlineStr"/>
@@ -13307,10 +13307,10 @@
         <v>70236.84</v>
       </c>
       <c r="O182" s="19" t="n">
-        <v>45796.85</v>
+        <v>46000.35</v>
       </c>
       <c r="P182" s="19" t="n">
-        <v>119.26</v>
+        <v>119.17</v>
       </c>
     </row>
   </sheetData>
@@ -14677,16 +14677,16 @@
         <v>214</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>42.5</v>
+        <v>43</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>264.5</v>
+        <v>265</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G5" s="16" t="n">
         <v>592.2</v>
@@ -14707,13 +14707,13 @@
         <v>103.25</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>116.75</v>
+        <v>118.25</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>15</v>
@@ -14723,7 +14723,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -14735,7 +14735,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>121.75</v>
+        <v>124.75</v>
       </c>
     </row>
   </sheetData>
@@ -14820,10 +14820,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>375126</v>
+        <v>376762</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>171397</v>
+        <v>173034</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>203729</v>
@@ -14845,10 +14845,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>195795</v>
+        <v>197635</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>90915</v>
+        <v>92755</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104880</v>
@@ -14870,10 +14870,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>179331</v>
+        <v>179127</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>80482</v>
+        <v>80279</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>98848</v>
@@ -15827,7 +15827,7 @@
         </is>
       </c>
       <c r="I23" s="26" t="n">
-        <v>0</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="24">
@@ -16249,7 +16249,7 @@
         </is>
       </c>
       <c r="I33" s="25" t="n">
-        <v>75580</v>
+        <v>77420</v>
       </c>
     </row>
     <row r="34">
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="I34" s="25" t="n">
-        <v>33194</v>
+        <v>35034</v>
       </c>
     </row>
     <row r="35">
@@ -16305,7 +16305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -16326,7 +16326,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>17 clôture(s) : 13 projet(s), 4 rework</t>
+          <t>18 clôture(s) : 14 projet(s), 4 rework</t>
         </is>
       </c>
     </row>
@@ -16576,17 +16576,17 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32357</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CESTAS] - Accomp 1/2j</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CESTAS</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -16600,28 +16600,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-16171</t>
+          <t>PDMDEP-32357</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>[RODEZ] Littéralis expert</t>
+          <t>[COMMUNE DE CESTAS] - Accomp 1/2j</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>RODEZ</t>
+          <t>COMMUNE DE CESTAS</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E13" s="16" t="inlineStr">
@@ -16630,23 +16630,23 @@
         </is>
       </c>
       <c r="F13" s="16" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-17291</t>
+          <t>PDMDEP-16171</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>[EVREUX] Littéralis Expert</t>
+          <t>[RODEZ] Littéralis expert</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[EVREUX] </t>
+          <t>RODEZ</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -16660,23 +16660,23 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-31285</t>
+          <t>PDMDEP-17291</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffr</t>
+          <t>[EVREUX] Littéralis Expert</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t xml:space="preserve">[EVREUX] </t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
@@ -16690,23 +16690,23 @@
         </is>
       </c>
       <c r="F15" s="16" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32009</t>
+          <t>PDMDEP-31285</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [TULLE AGGLO] Accomp modélisation</t>
+          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffr</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>COMMUNAUTE D'AGGLOMERATION TULLE AGGLO</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -16720,83 +16720,83 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
+          <t>PDMDEP-32009</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [TULLE AGGLO] Accomp modélisation</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>COMMUNAUTE D'AGGLOMERATION TULLE AGGLO</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
           <t>PDMDEP-33471</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>COMMUNE D AUCH</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="n">
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>PDMDEP-17131</t>
-        </is>
-      </c>
-      <c r="B18" s="28" t="inlineStr">
-        <is>
-          <t>[PAU] Migration GEODP</t>
-        </is>
-      </c>
-      <c r="C18" s="28" t="inlineStr">
-        <is>
-          <t>PAU</t>
-        </is>
-      </c>
-      <c r="D18" s="28" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="F18" s="28" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="28" t="inlineStr">
         <is>
-          <t>PDMDEP-21265</t>
+          <t>PDMDEP-17131</t>
         </is>
       </c>
       <c r="B19" s="28" t="inlineStr">
         <is>
-          <t>[Sanary sur Mer] Migration Placier + nouveaux modules avec r</t>
+          <t>[PAU] Migration GEODP</t>
         </is>
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>SANARY SUR MER</t>
+          <t>PAU</t>
         </is>
       </c>
       <c r="D19" s="28" t="inlineStr">
@@ -16810,28 +16810,28 @@
         </is>
       </c>
       <c r="F19" s="28" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="28" t="inlineStr">
         <is>
-          <t>PDMDEP-23410</t>
+          <t>PDMDEP-21265</t>
         </is>
       </c>
       <c r="B20" s="28" t="inlineStr">
         <is>
-          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
+          <t>[Sanary sur Mer] Migration Placier + nouveaux modules avec r</t>
         </is>
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>[EVREUX PORTES DE NORMANDIE]</t>
+          <t>SANARY SUR MER</t>
         </is>
       </c>
       <c r="D20" s="28" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E20" s="28" t="inlineStr">
@@ -16840,65 +16840,95 @@
         </is>
       </c>
       <c r="F20" s="28" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="28" t="inlineStr">
         <is>
+          <t>PDMDEP-23410</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>[EVREUX PORTES DE NORMANDIE]</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
           <t>PDMDEP-24216</t>
         </is>
       </c>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
         </is>
       </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E22" s="28" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n">
+      <c r="F22" s="28" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n"/>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n"/>
-      <c r="C24" s="29" t="n"/>
-      <c r="D24" s="29" t="n"/>
-      <c r="E24" s="29" t="n"/>
-      <c r="F24" s="29" t="n">
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n">
         <v>4</v>
       </c>
     </row>
